--- a/bowl_chicken.xlsx
+++ b/bowl_chicken.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralesupelec-my.sharepoint.com/personal/benjamin_dieu2_student-cs_fr/Documents/EXTRA/HEALTH_FITNESS/Recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30EA4CA5-A7D6-D34D-A134-5BA10F5C2AA1}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85DFD0F5-14FA-CD4D-AB1B-E77814C28867}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="660" windowWidth="17980" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6920" yWindow="660" windowWidth="17980" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipe" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>Red onion</t>
   </si>
   <si>
-    <t>Pepper</t>
-  </si>
-  <si>
     <t>Black beans</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>Cook for another 2 minutes. Mix in cilantro if using and remove from heat. Sprinkle with feta cheese if desired then serve and enjoy!</t>
+  </si>
+  <si>
+    <t>Bell pepper</t>
   </si>
 </sst>
 </file>
@@ -595,7 +595,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -654,7 +654,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -679,7 +679,7 @@
         <v>19.5</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -704,12 +704,12 @@
         <v>2.19</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7">
         <v>0.5</v>
@@ -730,18 +730,18 @@
         <v>1.0933333333333333</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7">
         <v>0.25</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -756,18 +756,18 @@
         <v>1.38</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="11">
         <v>0.5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -781,12 +781,12 @@
         <v>5.97</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="11">
         <v>25</v>
@@ -803,12 +803,12 @@
         <v>g</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="11">
         <v>100</v>

--- a/bowl_chicken.xlsx
+++ b/bowl_chicken.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralesupelec-my.sharepoint.com/personal/benjamin_dieu2_student-cs_fr/Documents/EXTRA/HEALTH_FITNESS/Recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85DFD0F5-14FA-CD4D-AB1B-E77814C28867}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAB85F5-5928-6642-BD2B-AF85B942D9D2}"/>
   <bookViews>
     <workbookView xWindow="6920" yWindow="660" windowWidth="17980" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipe" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -272,15 +272,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -586,19 +586,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.05859375" customWidth="1"/>
+    <col min="2" max="3" width="11.97265625" customWidth="1"/>
+    <col min="4" max="4" width="17.62109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -653,7 +653,7 @@
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>19</v>
       </c>
     </row>
@@ -678,7 +678,7 @@
       <c r="F5">
         <v>19.5</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -687,14 +687,14 @@
         <v>11</v>
       </c>
       <c r="B6" s="9">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="14" t="str">
         <f t="shared" si="1"/>
@@ -738,14 +738,14 @@
         <v>12</v>
       </c>
       <c r="B8" s="7">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E8" s="14" t="str">
         <f t="shared" si="1"/>
@@ -755,7 +755,7 @@
         <f>0.69*2</f>
         <v>1.38</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>23</v>
       </c>
     </row>

--- a/bowl_chicken.xlsx
+++ b/bowl_chicken.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralesupelec-my.sharepoint.com/personal/benjamin_dieu2_student-cs_fr/Documents/EXTRA/HEALTH_FITNESS/Recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAB85F5-5928-6642-BD2B-AF85B942D9D2}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{0FA07D17-894C-9045-B182-09C59D898DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F82E3261-F36B-8445-B56A-C0D1457B6309}"/>
   <bookViews>
     <workbookView xWindow="6920" yWindow="660" windowWidth="17980" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -712,14 +712,14 @@
         <v>26</v>
       </c>
       <c r="B7" s="7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E7" s="14" t="str">
         <f t="shared" si="1"/>
